--- a/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T08:56:46+00:00</t>
+    <t>2026-07-14T09:07:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
+++ b/r4-ELGA-e-Medikation-uc_5_6/StructureDefinition-at-elga-emed-medicationdispense-durchgefuehrteabgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:07:25+00:00</t>
+    <t>2026-07-16T16:15:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
